--- a/artfynd/A 21488-2022 artfynd.xlsx
+++ b/artfynd/A 21488-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,596 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114884162</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57764</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bladmoren, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>614141</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6778808</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114883527</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bladmoren, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>614228</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6778668</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114883157</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bladmoren, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>614232</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6778684</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114883731</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57764</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bladmoren, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>614256</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6778844</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114883340</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bladmoren, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>614156</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6778802</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21488-2022 artfynd.xlsx
+++ b/artfynd/A 21488-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114883157</v>
+        <v>129316547</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,32 +705,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bladmoren, Hls</t>
+          <t>Långsva, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614232</v>
+        <v>614134</v>
       </c>
       <c r="R2" t="n">
-        <v>6778684</v>
+        <v>6778982</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>06:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,54 +784,58 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114882027</v>
+        <v>114883731</v>
       </c>
       <c r="B3" t="n">
-        <v>97570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614282</v>
+        <v>614256</v>
       </c>
       <c r="R3" t="n">
-        <v>6778890</v>
+        <v>6778844</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,39 +899,38 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114883340</v>
+        <v>114884162</v>
       </c>
       <c r="B4" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,29 +943,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bladmoren, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614155</v>
+        <v>614142</v>
       </c>
       <c r="R4" t="n">
-        <v>6778802</v>
+        <v>6778808</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1022,32 +1015,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114883527</v>
+        <v>129315870</v>
       </c>
       <c r="B5" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1060,11 +1048,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1072,17 +1055,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bladmoren, Hls</t>
+          <t>Långsva, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614228</v>
+        <v>614291</v>
       </c>
       <c r="R5" t="n">
-        <v>6778668</v>
+        <v>6778962</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,17 +1084,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Skog</t>
+          <t>Söderala</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>04:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>04:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,48 +1124,43 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114884100</v>
+        <v>114883527</v>
       </c>
       <c r="B6" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1180,6 +1168,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1191,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614174</v>
+        <v>614228</v>
       </c>
       <c r="R6" t="n">
-        <v>6778811</v>
+        <v>6778668</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,7 +1239,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1257,37 +1250,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114883731</v>
+        <v>114884100</v>
       </c>
       <c r="B7" t="n">
-        <v>57792</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1295,11 +1283,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1311,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614256</v>
+        <v>614174</v>
       </c>
       <c r="R7" t="n">
-        <v>6778844</v>
+        <v>6778811</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,12 +1324,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1349,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1377,15 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114884162</v>
+        <v>114883157</v>
       </c>
       <c r="B8" t="n">
-        <v>57792</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,16 +1371,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1412,7 +1390,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,13 +1409,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614142</v>
+        <v>614232</v>
       </c>
       <c r="R8" t="n">
-        <v>6778808</v>
+        <v>6778684</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,12 +1439,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,14 +1464,471 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114883340</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bladmoren, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>614155</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6778802</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129314951</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>614156</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6778953</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129314952</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>614157</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6778960</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114882027</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bladmoren, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>614282</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6778890</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
           <t>Jake Bull</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21488-2022 artfynd.xlsx
+++ b/artfynd/A 21488-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Storgrundet - Klompletering NVI med Fåglar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129316547</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883731</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Storgrundet - Klompletering NVI med Fåglar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129315870</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883527</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883157</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1587,6 +1627,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883340</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,6 +1752,11 @@
           <t>Storgrundet - Klompletering NVI med Fåglar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314951</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1827,6 +1877,11 @@
           <t>Storgrundet - Klompletering NVI med Fåglar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314952</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1929,8 +1984,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114882027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>